--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="72">
   <si>
     <t>ProductID</t>
   </si>
@@ -176,7 +176,7 @@
     <t>rare_exp</t>
   </si>
   <si>
-    <t>ZhuBajie_avatar</t>
+    <t>ZhuBaJie</t>
   </si>
   <si>
     <t>supreme_exp</t>
@@ -1159,7 +1159,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14" t="s">
         <v>65</v>
@@ -1206,7 +1206,7 @@
         <v>120</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15" t="s">
         <v>65</v>
@@ -1253,7 +1253,7 @@
         <v>8000</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16" t="s">
         <v>65</v>
@@ -1300,7 +1300,7 @@
         <v>10000</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17" t="s">
         <v>65</v>
@@ -1489,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1527,54 +1527,54 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1582,13 +1582,79 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="C9">
+      <c r="C14">
         <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>ProductID</t>
   </si>
@@ -146,91 +146,94 @@
     <t>SunWukong</t>
   </si>
   <si>
+    <t>Armor01_Belt</t>
+  </si>
+  <si>
+    <t>TangSanZang</t>
+  </si>
+  <si>
+    <t>common_exp</t>
+  </si>
+  <si>
+    <t>Fried_Radish_Balls</t>
+  </si>
+  <si>
+    <t>Dragon_Bread_Noodies</t>
+  </si>
+  <si>
+    <t>Murshroom_Steamed_Buns</t>
+  </si>
+  <si>
+    <t>Tofu_Soup</t>
+  </si>
+  <si>
+    <t>Lamian_Noodies</t>
+  </si>
+  <si>
+    <t>fine_exp</t>
+  </si>
+  <si>
+    <t>rare_exp</t>
+  </si>
+  <si>
+    <t>ZhuBaJie</t>
+  </si>
+  <si>
+    <t>supreme_exp</t>
+  </si>
+  <si>
+    <t>Garnet_Gemstone</t>
+  </si>
+  <si>
+    <t>BUNDLE_JADE_01</t>
+  </si>
+  <si>
+    <t>BUNDLE_JADE_02</t>
+  </si>
+  <si>
+    <t>BUNDLE_COIN_01</t>
+  </si>
+  <si>
+    <t>BUNDLE_COIN_02</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Lifetime</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>BundleID</t>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
     <t>Nimbus_Cudgel</t>
-  </si>
-  <si>
-    <t>TangSanZang</t>
-  </si>
-  <si>
-    <t>common_exp</t>
-  </si>
-  <si>
-    <t>Fried_Radish_Balls</t>
-  </si>
-  <si>
-    <t>Dragon_Bread_Noodies</t>
-  </si>
-  <si>
-    <t>Murshroom_Steamed_Buns</t>
-  </si>
-  <si>
-    <t>Tofu_Soup</t>
-  </si>
-  <si>
-    <t>Lamian_Noodies</t>
-  </si>
-  <si>
-    <t>fine_exp</t>
-  </si>
-  <si>
-    <t>rare_exp</t>
-  </si>
-  <si>
-    <t>ZhuBaJie</t>
-  </si>
-  <si>
-    <t>supreme_exp</t>
-  </si>
-  <si>
-    <t>Garnet_Gemstone</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_01</t>
-  </si>
-  <si>
-    <t>BUNDLE_JADE_02</t>
-  </si>
-  <si>
-    <t>BUNDLE_COIN_01</t>
-  </si>
-  <si>
-    <t>BUNDLE_COIN_02</t>
-  </si>
-  <si>
-    <t>Jade</t>
-  </si>
-  <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>BundleID</t>
-  </si>
-  <si>
-    <t>ItemID</t>
-  </si>
-  <si>
-    <t>Amount</t>
   </si>
 </sst>
 </file>
@@ -1552,7 +1555,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>1</v>

--- a/Tool/data/Shop.xlsx
+++ b/Tool/data/Shop.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityUdeme\MyTemplate\MyTemplate\Tool\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
@@ -10,7 +15,7 @@
     <sheet name="ShopProducts" sheetId="1" r:id="rId1"/>
     <sheet name="BundleContents" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -239,8 +244,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +308,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -349,7 +362,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -381,9 +394,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -415,6 +429,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -590,11 +605,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -682,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -723,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -764,7 +779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -805,7 +820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -846,7 +861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -887,7 +902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -928,7 +943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -969,7 +984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1051,7 +1066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1092,7 +1107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1133,7 +1148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1180,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1227,7 +1242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1274,7 +1289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1321,7 +1336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1362,7 +1377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1403,7 +1418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1444,7 +1459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1491,11 +1506,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
@@ -1506,7 +1525,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -1517,7 +1536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1528,7 +1547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -1539,7 +1558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1550,7 +1569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -1561,7 +1580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -1572,7 +1591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1583,7 +1602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1594,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1605,7 +1624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1616,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1627,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1638,7 +1657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1649,7 +1668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>59</v>
       </c>
